--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487440_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487440_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8321</v>
+        <v>5.2742</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4477</v>
+        <v>4.4244</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3844</v>
+        <v>0.8498</v>
       </c>
       <c r="G2" t="n">
         <v>4.464</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2137</v>
+        <v>0.6558</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7399</v>
+        <v>-0.2835</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4739</v>
+        <v>0.9393</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.96</v>
+        <v>3.4763</v>
       </c>
       <c r="E3" t="n">
-        <v>1.309</v>
+        <v>1.7183</v>
       </c>
       <c r="F3" t="n">
-        <v>1.651</v>
+        <v>1.758</v>
       </c>
       <c r="G3" t="n">
         <v>0.924</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9433</v>
+        <v>-0.427</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0692</v>
+        <v>-0.6599</v>
       </c>
       <c r="U3" t="n">
-        <v>0.126</v>
+        <v>0.2329</v>
       </c>
       <c r="V3" t="n">
         <v>1.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2106</v>
+        <v>2.478</v>
       </c>
       <c r="E4" t="n">
         <v>1.5165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6942</v>
+        <v>0.9615</v>
       </c>
       <c r="G4" t="n">
         <v>1.9056</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0659</v>
+        <v>0.2014</v>
       </c>
       <c r="T4" t="n">
         <v>-0.5652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4993</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9034</v>
+        <v>2.1163</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0057</v>
+        <v>1.3909</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8977</v>
+        <v>0.7254</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6469</v>
+        <v>5.8763</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5969</v>
+        <v>3.1933</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9499</v>
+        <v>2.683</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5502</v>
+        <v>5.7733</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9803</v>
+        <v>3.2579</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4301</v>
+        <v>2.5154</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0968</v>
+        <v>0.103</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6166</v>
+        <v>-0.0646</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5198</v>
+        <v>0.1676</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6113</v>
+        <v>-0.427</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5652</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1765</v>
+        <v>0.3517</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5507</v>
+        <v>-2.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5507</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.707</v>
+        <v>1.8499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9816</v>
+        <v>0.0057</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7254</v>
+        <v>1.8442</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8763</v>
+        <v>1.6469</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1933</v>
+        <v>2.5969</v>
       </c>
       <c r="I6" t="n">
-        <v>2.683</v>
+        <v>-0.9499</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7733</v>
+        <v>1.5502</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2579</v>
+        <v>1.9803</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5154</v>
+        <v>-0.4301</v>
       </c>
       <c r="M6" t="n">
-        <v>0.103</v>
+        <v>0.0968</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0646</v>
+        <v>0.6166</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1676</v>
+        <v>-0.5198</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8363</v>
+        <v>0.5578</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.188</v>
+        <v>-0.5652</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3517</v>
+        <v>1.1231</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1578</v>
+        <v>-0.5507</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.492</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9063</v>
+        <v>0.9238</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1277</v>
+        <v>1.2971</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2213</v>
+        <v>-0.3733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2114</v>
+        <v>1.8052</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2266</v>
+        <v>2.2446</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0152</v>
+        <v>-0.4394</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3365</v>
+        <v>2.8563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.837</v>
+        <v>2.9227</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4994</v>
+        <v>-0.0664</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.125</v>
+        <v>-1.0511</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6781</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.373</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5668</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3447</v>
+        <v>-0.7064</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2088</v>
+        <v>-0.4464</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5535</v>
+        <v>-0.26</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2166</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4961</v>
+        <v>0.4565</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2971</v>
+        <v>1.0253</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.801</v>
+        <v>-0.5688</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8052</v>
+        <v>0.2114</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2446</v>
+        <v>0.2266</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4394</v>
+        <v>-0.0152</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8563</v>
+        <v>1.3365</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9227</v>
+        <v>0.837</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0664</v>
+        <v>0.4994</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0511</v>
+        <v>-1.125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6781</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.373</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.134</v>
+        <v>-0.1051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4464</v>
+        <v>-0.3111</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6876</v>
+        <v>0.206</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2166</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2191</v>
+        <v>-1.5959</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4421</v>
+        <v>-2.0328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.223</v>
+        <v>0.4368</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2782</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.1012</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.891</v>
+        <v>-0.4817</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1667</v>
+        <v>0.3805</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5367</v>
+        <v>-1.8112</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9527</v>
+        <v>-0.441</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.584</v>
+        <v>-1.3702</v>
       </c>
       <c r="G10" t="n">
         <v>0.4819</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0566</v>
+        <v>-0.3311</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2474</v>
+        <v>-0.7358</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1908</v>
+        <v>0.4046</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1578</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7307</v>
+        <v>-4.6387</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2388</v>
+        <v>-5.8528</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5081</v>
+        <v>1.214</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4653</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9085</v>
+        <v>0.0004</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2952</v>
+        <v>-0.3188</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6133</v>
+        <v>0.3192</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2154</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.528999999999998</v>
+        <v>8.529200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.051699999999999</v>
+        <v>3.051600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4775</v>
+        <v>5.477400000000001</v>
       </c>
       <c r="G12" t="n">
         <v>14.5718</v>
       </c>
       <c r="H12" t="n">
-        <v>6.463</v>
+        <v>6.462999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>8.109</v>
@@ -1375,7 +1375,7 @@
         <v>-4.1152</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3075000000000002</v>
+        <v>-0.3075</v>
       </c>
       <c r="O12" t="n">
         <v>-3.8077</v>
@@ -1390,19 +1390,19 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6822</v>
+        <v>-0.6824000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.1461</v>
+        <v>-5.1463</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4641</v>
+        <v>4.463900000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-8.298299999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.261599999999999</v>
+        <v>1.2616</v>
       </c>
       <c r="X12" t="n">
         <v>-9.560099999999998</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.962300000000001</v>
+        <v>9.1449</v>
       </c>
       <c r="E13" t="n">
-        <v>8.8505</v>
+        <v>8.9529</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1118</v>
+        <v>0.192</v>
       </c>
       <c r="G13" t="n">
         <v>3.808</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3087</v>
+        <v>0.4912</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.387</v>
+        <v>-0.2847</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6957</v>
+        <v>0.7759</v>
       </c>
       <c r="V13" t="n">
         <v>4.2581</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3647</v>
+        <v>0.9287</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0837</v>
+        <v>-0.3256</v>
       </c>
       <c r="F14" t="n">
-        <v>1.281</v>
+        <v>1.2543</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0408</v>
@@ -1546,13 +1546,13 @@
         <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4655</v>
+        <v>1.0294</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8893</v>
+        <v>0.4799</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5762</v>
+        <v>0.5495</v>
       </c>
       <c r="V14" t="n">
         <v>1.3318</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9062</v>
+        <v>0.8431</v>
       </c>
       <c r="E15" t="n">
-        <v>1.546</v>
+        <v>0.6659</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6398</v>
+        <v>0.1772</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2512</v>
+        <v>1.4981</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6145</v>
+        <v>-1.6043</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3634</v>
+        <v>3.1023</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1824</v>
+        <v>3.9782</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0208</v>
+        <v>0.0935</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1617</v>
+        <v>3.8847</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9312</v>
+        <v>-2.4801</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4062</v>
+        <v>-1.6978</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.525</v>
+        <v>-0.7823</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5875</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2079</v>
+        <v>0.2448</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0882</v>
+        <v>-0.6499</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2961</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ DÍEZ</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5475</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5629</v>
+        <v>1.1366</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0154</v>
+        <v>-0.5062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5977</v>
+        <v>0.2512</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3675</v>
+        <v>0.6145</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9651</v>
+        <v>-0.3634</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2581</v>
+        <v>1.1824</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6414</v>
+        <v>1.0208</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8995</v>
+        <v>0.1617</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6604</v>
+        <v>-0.9312</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2739</v>
+        <v>-0.4062</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9344</v>
+        <v>-0.525</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0293</v>
+        <v>-0.4836</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0882</v>
+        <v>-0.3211</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0589</v>
+        <v>-0.1625</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2754</v>
+        <v>0.2754</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>H. RODRÍGUEZ DÍEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1535</v>
+        <v>0.2184</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0504</v>
+        <v>2.1536</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2039</v>
+        <v>-1.9352</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4981</v>
+        <v>0.5977</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6043</v>
+        <v>-0.3675</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1023</v>
+        <v>0.9651</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9782</v>
+        <v>1.2581</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0935</v>
+        <v>-0.6414</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8847</v>
+        <v>1.8995</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4801</v>
+        <v>-0.6604</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6978</v>
+        <v>0.2739</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7823</v>
+        <v>-0.9344</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4448</v>
+        <v>-0.2998</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3662</v>
+        <v>-0.3211</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9214</v>
+        <v>0.0213</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2754</v>
+        <v>-0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7654</v>
+        <v>-0.3293</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7335</v>
+        <v>-0.3242</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0319</v>
+        <v>-0.0051</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4772</v>
@@ -1858,13 +1858,13 @@
         <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4092</v>
+        <v>0.0269</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0692</v>
+        <v>-0.6599</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6601</v>
+        <v>0.6868</v>
       </c>
       <c r="V18" t="n">
         <v>2.1003</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8663</v>
+        <v>-1.0397</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6211</v>
+        <v>-1.9281</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7547</v>
+        <v>0.8884</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4595</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2014</v>
+        <v>0.0281</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3852</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1838</v>
+        <v>-0.0501</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4234</v>
+        <v>-1.7434</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9722</v>
+        <v>-2.5862</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5488</v>
+        <v>0.8428</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6306</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7947</v>
+        <v>0.4748</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5023</v>
+        <v>-0.1118</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2925</v>
+        <v>0.5865</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5753</v>
+        <v>-3.0741</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6507</v>
+        <v>-2.8554</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07539999999999999</v>
+        <v>-0.2186</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2438</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0355</v>
+        <v>-0.5342</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8028</v>
+        <v>-1.0075</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7673</v>
+        <v>0.4733</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8031</v>
+        <v>-3.367</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5319</v>
+        <v>-2.1226</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2712</v>
+        <v>-1.2444</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2749</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9614</v>
+        <v>-0.5254</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.188</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2266</v>
+        <v>0.2533</v>
       </c>
       <c r="V22" t="n">
         <v>0.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.0298</v>
+        <v>-10.7411</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.960699999999999</v>
+        <v>-8.244300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0691</v>
+        <v>-2.4968</v>
       </c>
       <c r="G23" t="n">
         <v>-9.600099999999999</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0587</v>
+        <v>0.23</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6039</v>
+        <v>-0.8875</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5452</v>
+        <v>1.1175</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.5291</v>
+        <v>-8.529</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.477399999999999</v>
+        <v>-5.477400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.051800000000001</v>
+        <v>-3.0516</v>
       </c>
       <c r="G24" t="n">
         <v>-14.5719</v>
@@ -2299,13 +2299,13 @@
         <v>-8.109099999999998</v>
       </c>
       <c r="J24" t="n">
-        <v>4.115300000000003</v>
+        <v>4.1153</v>
       </c>
       <c r="K24" t="n">
         <v>0.3074999999999994</v>
       </c>
       <c r="L24" t="n">
-        <v>3.807799999999999</v>
+        <v>3.807800000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-18.6871</v>
@@ -2326,10 +2326,10 @@
         <v>11.7507</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6820999999999997</v>
+        <v>0.6822000000000003</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.463900000000001</v>
+        <v>-4.4641</v>
       </c>
       <c r="U24" t="n">
         <v>5.1462</v>
